--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão (1).xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão (1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7741CD58-A26C-4E65-82DD-6F559B37FAE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F09848EC-AD1D-46CB-8679-AF00A0F64C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28935" windowHeight="14685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28935" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="142">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -62,181 +62,451 @@
     <t>juliana.diniz@allianz.com.br</t>
   </si>
   <si>
-    <t>aline.nogueira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12828261200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>bruna.silva1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13012351800000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>daniel.lourenco@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13058307800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>mariana.dolence@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12649010900000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
     <t>danillo.boem@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-22019416883 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>fernando.martins1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12782508100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>lidiane.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12620116300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12782253400001 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12782253400004 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12782253400008 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13018499600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-21859480000110 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>carla.ventura@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13037182600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>viviane.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13048136000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>angela.carmo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13056861600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>luciana.belisario@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13041238600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>andriele.pala@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13063397600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>talita.meneses@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13046485400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>gustavo.correa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13005681600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>raullison.castro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13057699600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>marco.vita@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12675415400000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13061231700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13062493000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
     <t>rafael.leite@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12786242000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>thays.silva@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12898883200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>leticia.bezerra@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13057563200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>leinny.amorim@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13054244100000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>laila.steil@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-88819135600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12620116300000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12863648600000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13055033700000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13057424100000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>danieli.ferreira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13047570300000 Nota 738 - Erro Voucher - exclusivo Operações</t>
-  </si>
-  <si>
-    <t>janaina.cazelato@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12878384200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>juscara.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13044377600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>sidney.cruz@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13059364300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>lilian.sudati@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12816435200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>adriano.guerra@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12833392300000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>danielle.nascimento@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13057528700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>kaue.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13063183300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>patricia.reis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13054896300000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13059382600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>samuel.martins@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12704095300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13057318500000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>claudia.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12900518500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12900659700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12902624500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>vanessa.campos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13055626500000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>kaue.medeiros@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12860737300000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13048072600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>sonia.bortoleto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12728519700000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>cleyciane.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12877731000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>daniela.gui@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13047435900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>renata.matheus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13052767800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13053853000000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>andre.gouvea@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12917404900000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>viviane.corbari@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12800835100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>andrea.duarte@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12919258200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>flavia.costa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13062611100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>ana.cunha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-33892738000160 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>luiz.sanchetta@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12793884300002 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>claudia.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12867914200000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13061126300000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13061625700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13063954900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13064149000000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>adalberto.souza@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13063757700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12742243200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13062813200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>joao.neto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13054020100000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>natalia.soares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12618395200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12631262600000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13044019200000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13044475900000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13044936700000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13046723800000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13053063600000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13059581400000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>carla.catalani@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13028091800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>silvia.plaza@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12862416400000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>l3corretoraseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127264181 - DANILO VINICIUS DE OLIVEIRA COSTA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 9 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>alliancaseguros1@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127367133 - VALERIA MARIA DE MEDEIROS RANGEL TRAVASSOS</t>
+  </si>
+  <si>
+    <t>diretoria@lapisbellus.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127377645 - ILIDIO DE JESUS COELHO</t>
+  </si>
+  <si>
+    <t>suporte.vvd@vwfs.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127367989 - FELIPE CAMILO CARDOSO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>backofficeseguros@vwfs.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127390967 - RITA DE CASSIA CORREA PESSOA</t>
+  </si>
+  <si>
+    <t>emissao@sicoobminaseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127354937 - SIMONIE TEIXEIRA BORGES</t>
+  </si>
+  <si>
+    <t>paulo.neime@complex.net.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127668999 - MARIA GORETTI MELO BROWN SANTANA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>aliancadowsley@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127714653 - JOSE MARTINS DA SILVA JUNIOR</t>
+  </si>
+  <si>
+    <t>renovacaoseguros@honda.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127716778 - ADEILDO JOSE MARQUES BARRETO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127718928 - WESLEI BATISTA ALMEIDA</t>
+  </si>
+  <si>
+    <t>pendencias@rbmseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127920995 - SUELI DAS GRACAS MONTEIRO DA SILVA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>contato@wecorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127990636 - GILSOM RICARDO MARCONI DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>verdecapseguros@outlook.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127971884 - SILVIA PEREIRA DE SOUSA SILVEIRA</t>
+  </si>
+  <si>
+    <t>backofficecorretora@segurostoyota.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127945266 - MARLENE NUNES GOMES RICATTO</t>
+  </si>
+  <si>
+    <t>operacional@seguroo.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128045838 - ROSANA THOME</t>
+  </si>
+  <si>
+    <t>rybel.seguros@terra.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128016838 - ADRIANA YUMI NAKATSU</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127968570 - THIANA DA SILVA CERQUEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128051737 - WELLINGTON JOSE DA SILVA</t>
+  </si>
+  <si>
+    <t>jethaseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128445075 - SARA ELZA CALDAS DE SANTANA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 6 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>unitas@unitasnet.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128457500 - JENIEL RODRIGUES DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>pendencia@seguralta.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128880075 - KELLY BARNABE SERPA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>allianz@redelojacorr.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128928907 - ANDREIA PEREIRA DIAS</t>
+  </si>
+  <si>
+    <t>corretora@pessego.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128919037 - HAMILTON IMACULADO CONCEICAO SILVA</t>
+  </si>
+  <si>
+    <t>madre@madreseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128929454 - CRISTIANO FADEL FERNANDES DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>ativa@ativaseguros.net</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128908206 - TATIANA FERREIRA ANGST</t>
+  </si>
+  <si>
+    <t>contato@ivsseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129359367 - JOAO PAULO MAIA DE ALENCAR TAVARES</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>ajs_corretordeseguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126721349 - MANOEL MESSIAS PINHEIRO DA SILVA</t>
+  </si>
+  <si>
+    <t>emissao@segurosarinos.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129795396 - ELSO RODRIGUES</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129728584 - FRANCISCO DAVID JARDILINO BARBOSA</t>
   </si>
 </sst>
 </file>
@@ -636,10 +906,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -647,10 +917,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -658,10 +928,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -669,10 +939,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -680,10 +950,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -691,10 +961,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -702,10 +972,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -713,10 +983,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -724,10 +994,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -735,10 +1005,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -746,10 +1016,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -757,10 +1027,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -768,10 +1038,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -779,10 +1049,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -790,10 +1060,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -801,10 +1071,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -812,10 +1082,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -823,10 +1093,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -834,10 +1104,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -845,10 +1115,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -856,10 +1126,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -867,10 +1137,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -878,10 +1148,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
@@ -889,10 +1159,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -900,10 +1170,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -911,10 +1181,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -922,10 +1192,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
@@ -933,10 +1203,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>3</v>
@@ -944,10 +1214,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>3</v>
@@ -955,10 +1225,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>3</v>
@@ -966,10 +1236,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>3</v>
@@ -977,10 +1247,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="B33" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>3</v>
@@ -988,10 +1258,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>3</v>
@@ -999,10 +1269,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>3</v>
@@ -1010,187 +1280,460 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B36" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37"/>
-      <c r="B37"/>
+      <c r="A37" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38"/>
-      <c r="B38"/>
+      <c r="A38" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39"/>
-      <c r="B39"/>
+      <c r="A39" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40"/>
-      <c r="B40"/>
+      <c r="A40" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" t="s">
+        <v>72</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41"/>
-      <c r="B41"/>
+      <c r="A41" t="s">
+        <v>5</v>
+      </c>
+      <c r="B41" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42"/>
-      <c r="B42"/>
+      <c r="A42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" t="s">
+        <v>74</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43"/>
-      <c r="B43"/>
+      <c r="A43" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" t="s">
+        <v>75</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44"/>
-      <c r="B44"/>
+      <c r="A44" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" t="s">
+        <v>76</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45"/>
-      <c r="B45"/>
+      <c r="A45" t="s">
+        <v>77</v>
+      </c>
+      <c r="B45" t="s">
+        <v>78</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46"/>
-      <c r="B46"/>
+      <c r="A46" t="s">
+        <v>79</v>
+      </c>
+      <c r="B46" t="s">
+        <v>80</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47"/>
-      <c r="B47"/>
+      <c r="A47" t="s">
+        <v>81</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48"/>
-      <c r="B48"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49"/>
-      <c r="B49"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50"/>
-      <c r="B50"/>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51"/>
-      <c r="B51"/>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52"/>
-      <c r="B52"/>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53"/>
-      <c r="B53"/>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54"/>
-      <c r="B54"/>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55"/>
-      <c r="B55"/>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56"/>
-      <c r="B56"/>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57"/>
-      <c r="B57"/>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58"/>
-      <c r="B58"/>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59"/>
-      <c r="B59"/>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60"/>
-      <c r="B60"/>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61"/>
-      <c r="B61"/>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62"/>
-      <c r="B62"/>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63"/>
-      <c r="B63"/>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64"/>
-      <c r="B64"/>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65"/>
-      <c r="B65"/>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66"/>
-      <c r="B66"/>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67"/>
-      <c r="B67"/>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68"/>
-      <c r="B68"/>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69"/>
-      <c r="B69"/>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70"/>
-      <c r="B70"/>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71"/>
-      <c r="B71"/>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72"/>
-      <c r="B72"/>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73"/>
-      <c r="B73"/>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74"/>
-      <c r="B74"/>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75"/>
-      <c r="B75"/>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>84</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>86</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>88</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>90</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>92</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>94</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>97</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>99</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>99</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>102</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>105</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>107</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>109</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>111</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>113</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>99</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>99</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>117</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>120</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>122</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>125</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>127</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>129</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>131</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>133</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>136</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>138</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>99</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76"/>
       <c r="B76"/>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77"/>
       <c r="B77"/>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78"/>
       <c r="B78" s="3"/>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79"/>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80"/>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
